--- a/data/24August-Gold_Diggers-v-Oaks.xlsx
+++ b/data/24August-Gold_Diggers-v-Oaks.xlsx
@@ -166,7 +166,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:O161"/>
   <sheetData>
     <row r="1">
@@ -1323,8 +1323,10 @@
       <c r="D123" t="s">
         <v>19</v>
       </c>
-      <c r="E123" t="s">
-        <v>42</v>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>UCDC</t>
+        </is>
       </c>
     </row>
     <row r="124">
@@ -1607,8 +1609,10 @@
       <c r="D154" t="s">
         <v>19</v>
       </c>
-      <c r="E154" t="s">
-        <v>47</v>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>DCLC</t>
+        </is>
       </c>
     </row>
     <row r="155">
@@ -1624,8 +1628,10 @@
       <c r="D155" t="s">
         <v>19</v>
       </c>
-      <c r="E155" t="s">
-        <v>49</v>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>LCDC</t>
+        </is>
       </c>
     </row>
     <row r="156">
